--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_TOPSURFACE NB PATERNA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_TOPSURFACE NB PATERNA.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>87.9012</v>
+        <v>96.6562</v>
       </c>
       <c r="E2" t="n">
-        <v>54.9042</v>
+        <v>60.703</v>
       </c>
       <c r="F2" t="n">
-        <v>32.9973</v>
+        <v>35.9535</v>
       </c>
       <c r="G2" t="n">
         <v>60.6072</v>
@@ -610,13 +610,13 @@
         <v>60.1082</v>
       </c>
       <c r="S2" t="n">
-        <v>-4.379599999999999</v>
+        <v>4.3751</v>
       </c>
       <c r="T2" t="n">
-        <v>-7.0436</v>
+        <v>-1.2452</v>
       </c>
       <c r="U2" t="n">
-        <v>2.6644</v>
+        <v>5.6206</v>
       </c>
       <c r="V2" t="n">
         <v>13.1643</v>
@@ -643,13 +643,13 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>69.19799999999999</v>
+        <v>65.8434</v>
       </c>
       <c r="E3" t="n">
-        <v>42.9734</v>
+        <v>36.0521</v>
       </c>
       <c r="F3" t="n">
-        <v>26.2247</v>
+        <v>29.7918</v>
       </c>
       <c r="G3" t="n">
         <v>34.7376</v>
@@ -688,13 +688,13 @@
         <v>52.4115</v>
       </c>
       <c r="S3" t="n">
-        <v>13.2334</v>
+        <v>9.8787</v>
       </c>
       <c r="T3" t="n">
-        <v>11.6636</v>
+        <v>4.7421</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5699</v>
+        <v>5.1363</v>
       </c>
       <c r="V3" t="n">
         <v>11.6976</v>
@@ -721,13 +721,13 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>46.0335</v>
+        <v>45.1255</v>
       </c>
       <c r="E4" t="n">
-        <v>16.515</v>
+        <v>17.8079</v>
       </c>
       <c r="F4" t="n">
-        <v>29.5188</v>
+        <v>27.3177</v>
       </c>
       <c r="G4" t="n">
         <v>22.4662</v>
@@ -766,13 +766,13 @@
         <v>54.2443</v>
       </c>
       <c r="S4" t="n">
-        <v>9.3619</v>
+        <v>8.4534</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2535000000000005</v>
+        <v>1.0391</v>
       </c>
       <c r="U4" t="n">
-        <v>9.615600000000001</v>
+        <v>7.4145</v>
       </c>
       <c r="V4" t="n">
         <v>6.692</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. BAEZA CABRERA</t>
+          <t>E. CHOFRE TARREGA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>7.3856</v>
+        <v>8.646399999999998</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.882100000000001</v>
+        <v>-1.1863</v>
       </c>
       <c r="F6" t="n">
-        <v>10.2676</v>
+        <v>9.8329</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.221699999999999</v>
+        <v>-2.5807</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.2964</v>
+        <v>-0.8766999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0749</v>
+        <v>-1.704199999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>15.1259</v>
+        <v>9.8011</v>
       </c>
       <c r="K6" t="n">
-        <v>5.6801</v>
+        <v>8.9367</v>
       </c>
       <c r="L6" t="n">
-        <v>9.445499999999999</v>
+        <v>0.8644000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-17.3472</v>
+        <v>-12.3819</v>
       </c>
       <c r="N6" t="n">
-        <v>-8.976699999999999</v>
+        <v>-9.8133</v>
       </c>
       <c r="O6" t="n">
-        <v>-8.370700000000001</v>
+        <v>-2.5686</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.016</v>
+        <v>4.2149</v>
       </c>
       <c r="Q6" t="n">
-        <v>-32.2536</v>
+        <v>-20.8914</v>
       </c>
       <c r="R6" t="n">
-        <v>30.2374</v>
+        <v>25.106</v>
       </c>
       <c r="S6" t="n">
-        <v>14.8612</v>
+        <v>6.0637</v>
       </c>
       <c r="T6" t="n">
-        <v>4.3068</v>
+        <v>1.3155</v>
       </c>
       <c r="U6" t="n">
-        <v>10.5545</v>
+        <v>4.7479</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.2381</v>
+        <v>0.9492000000000004</v>
       </c>
       <c r="W6" t="n">
-        <v>9.9384</v>
+        <v>8.5885</v>
       </c>
       <c r="X6" t="n">
-        <v>-13.1767</v>
+        <v>-7.6394</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. MELGAR GARCIA</t>
+          <t>H. FABREGAT LORES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>4.8563</v>
+        <v>7.8238</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1423999999999997</v>
+        <v>-6.1104</v>
       </c>
       <c r="F7" t="n">
-        <v>4.9984</v>
+        <v>13.9342</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4596</v>
+        <v>26.0852</v>
       </c>
       <c r="H7" t="n">
-        <v>3.7251</v>
+        <v>16.9529</v>
       </c>
       <c r="I7" t="n">
-        <v>-5.1845</v>
+        <v>9.132200000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>8.001099999999999</v>
+        <v>28.4299</v>
       </c>
       <c r="K7" t="n">
-        <v>10.7781</v>
+        <v>18.0085</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.777</v>
+        <v>10.4215</v>
       </c>
       <c r="M7" t="n">
-        <v>-9.4605</v>
+        <v>-2.3449</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.0532</v>
+        <v>-1.0558</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.4072</v>
+        <v>-1.2892</v>
       </c>
       <c r="P7" t="n">
-        <v>4.0316</v>
+        <v>-1.4662</v>
       </c>
       <c r="Q7" t="n">
-        <v>-20.7083</v>
+        <v>-44.1654</v>
       </c>
       <c r="R7" t="n">
-        <v>24.7397</v>
+        <v>42.6989</v>
       </c>
       <c r="S7" t="n">
-        <v>13.2979</v>
+        <v>1.0509</v>
       </c>
       <c r="T7" t="n">
-        <v>13.0521</v>
+        <v>-4.3741</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2457</v>
+        <v>5.4253</v>
       </c>
       <c r="V7" t="n">
-        <v>-11.014</v>
+        <v>-17.8458</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.4875999999999998</v>
+        <v>13.9989</v>
       </c>
       <c r="X7" t="n">
-        <v>-10.5261</v>
+        <v>-31.845</v>
       </c>
     </row>
     <row r="8">
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. FABREGAT LORES</t>
+          <t>P. GARCIA BOSCH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>1.161</v>
+        <v>2.576</v>
       </c>
       <c r="E9" t="n">
-        <v>-11.5232</v>
+        <v>-2.9255</v>
       </c>
       <c r="F9" t="n">
-        <v>12.6843</v>
+        <v>5.5018</v>
       </c>
       <c r="G9" t="n">
-        <v>26.0852</v>
+        <v>3.687500000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>16.9529</v>
+        <v>4.053</v>
       </c>
       <c r="I9" t="n">
-        <v>9.132200000000001</v>
+        <v>-0.3656000000000002</v>
       </c>
       <c r="J9" t="n">
-        <v>28.4299</v>
+        <v>8.639200000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>18.0085</v>
+        <v>7.433</v>
       </c>
       <c r="L9" t="n">
-        <v>10.4215</v>
+        <v>1.2063</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3449</v>
+        <v>-4.9516</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0558</v>
+        <v>-3.3799</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2892</v>
+        <v>-1.5717</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.4662</v>
+        <v>-8.246600000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-44.1654</v>
+        <v>-18.3258</v>
       </c>
       <c r="R9" t="n">
-        <v>42.6989</v>
+        <v>10.0792</v>
       </c>
       <c r="S9" t="n">
-        <v>-5.612399999999999</v>
+        <v>-0.1011999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-9.7875</v>
+        <v>-1.2048</v>
       </c>
       <c r="U9" t="n">
-        <v>4.1753</v>
+        <v>1.1034</v>
       </c>
       <c r="V9" t="n">
-        <v>-17.8458</v>
+        <v>7.2364</v>
       </c>
       <c r="W9" t="n">
-        <v>13.9989</v>
+        <v>7.9654</v>
       </c>
       <c r="X9" t="n">
-        <v>-31.845</v>
+        <v>-0.7291000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. GARCIA BOSCH</t>
+          <t>H. PINAZO NAVARRO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2046000000000009</v>
+        <v>0.1791</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.6982</v>
+        <v>-0.2062999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>4.9029</v>
+        <v>0.3853</v>
       </c>
       <c r="G10" t="n">
-        <v>3.687500000000001</v>
+        <v>-0.2196</v>
       </c>
       <c r="H10" t="n">
-        <v>4.053</v>
+        <v>-0.2292</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3656000000000002</v>
+        <v>0.009599999999999997</v>
       </c>
       <c r="J10" t="n">
-        <v>8.639200000000001</v>
+        <v>-0.1783999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>7.433</v>
+        <v>-0.2201</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2063</v>
+        <v>0.0417</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.9516</v>
+        <v>-0.04129999999999995</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.3799</v>
+        <v>-0.009200000000000014</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.5717</v>
+        <v>-0.03209999999999996</v>
       </c>
       <c r="P10" t="n">
-        <v>-8.246600000000001</v>
+        <v>0.733</v>
       </c>
       <c r="Q10" t="n">
-        <v>-18.3258</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>10.0792</v>
+        <v>0.733</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.4727</v>
+        <v>-0.3343</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.9773</v>
+        <v>-0.0279</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5045999999999999</v>
+        <v>-0.3064</v>
       </c>
       <c r="V10" t="n">
-        <v>7.2364</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>7.9654</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.7291000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H. PINAZO NAVARRO</t>
+          <t>D. HOYAS PEREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1371</v>
+        <v>0.06339999999999946</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3986</v>
+        <v>-2.183599999999998</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2614000000000001</v>
+        <v>2.2472</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2196</v>
+        <v>-7.183000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2292</v>
+        <v>-11.2302</v>
       </c>
       <c r="I11" t="n">
-        <v>0.009599999999999997</v>
+        <v>4.047699999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1783999999999999</v>
+        <v>11.6564</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2201</v>
+        <v>0.5519000000000014</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0417</v>
+        <v>11.1045</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.04129999999999995</v>
+        <v>-18.839</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.009200000000000014</v>
+        <v>-11.7822</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.03209999999999996</v>
+        <v>-7.0567</v>
       </c>
       <c r="P11" t="n">
-        <v>0.733</v>
+        <v>-2.3822</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-33.9029</v>
       </c>
       <c r="R11" t="n">
-        <v>0.733</v>
+        <v>31.52</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6504</v>
+        <v>-3.1746</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2202</v>
+        <v>-3.5222</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4302</v>
+        <v>0.3479</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>12.8027</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>23.5844</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-10.7817</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. BLASCO BOJO</t>
+          <t>H. BAEZA CABRERA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.8015</v>
+        <v>-0.2276999999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7295</v>
+        <v>-6.7267</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.07199999999999999</v>
+        <v>6.4989</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7079</v>
+        <v>-2.221699999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7079</v>
+        <v>-3.2964</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1.0749</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6194</v>
+        <v>15.1259</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6194</v>
+        <v>5.6801</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>9.445499999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0885</v>
+        <v>-17.3472</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0885</v>
+        <v>-8.976699999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-8.370700000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-2.016</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-32.2536</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>30.2374</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0936</v>
+        <v>7.2477</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1101</v>
+        <v>0.4616999999999998</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0165</v>
+        <v>6.7859</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-3.2381</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>9.9384</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-13.1767</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.8922</v>
+        <v>-0.5294</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3039</v>
+        <v>-0.0154</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5883</v>
+        <v>-0.514</v>
       </c>
       <c r="G13" t="n">
         <v>-0.7947</v>
@@ -1468,13 +1468,13 @@
         <v>0.3665</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.464</v>
+        <v>-0.1012</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4404</v>
+        <v>-0.152</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0236</v>
+        <v>0.0507</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. ROMERA GALINDO</t>
+          <t>F. BLASCO BOJO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,61 +1498,61 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.975</v>
+        <v>-0.7766999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.4073</v>
+        <v>-0.7295</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5677</v>
+        <v>-0.0472</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.9915</v>
+        <v>-0.7079</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.4882</v>
+        <v>-0.7079</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5032</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.132</v>
+        <v>-0.6194</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.5327</v>
+        <v>-0.6194</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5994</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8594999999999999</v>
+        <v>-0.0885</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9555</v>
+        <v>-0.0885</v>
       </c>
       <c r="O14" t="n">
-        <v>0.09610000000000002</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8997999999999999</v>
+        <v>-0.0688</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2753</v>
+        <v>-0.1101</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6244999999999999</v>
+        <v>0.0413</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. CHOFRE TARREGA</t>
+          <t>A. MELGAR GARCIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.154000000000001</v>
+        <v>-1.445200000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.6327</v>
+        <v>-8.026</v>
       </c>
       <c r="F15" t="n">
-        <v>6.4786</v>
+        <v>6.581</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.5807</v>
+        <v>-1.4596</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8766999999999999</v>
+        <v>3.7251</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.704199999999999</v>
+        <v>-5.1845</v>
       </c>
       <c r="J15" t="n">
-        <v>9.8011</v>
+        <v>8.001099999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>8.9367</v>
+        <v>10.7781</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8644000000000001</v>
+        <v>-2.777</v>
       </c>
       <c r="M15" t="n">
-        <v>-12.3819</v>
+        <v>-9.4605</v>
       </c>
       <c r="N15" t="n">
-        <v>-9.8133</v>
+        <v>-7.0532</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.5686</v>
+        <v>-2.4072</v>
       </c>
       <c r="P15" t="n">
-        <v>4.2149</v>
+        <v>4.0316</v>
       </c>
       <c r="Q15" t="n">
-        <v>-20.8914</v>
+        <v>-20.7083</v>
       </c>
       <c r="R15" t="n">
-        <v>25.106</v>
+        <v>24.7397</v>
       </c>
       <c r="S15" t="n">
-        <v>-4.737</v>
+        <v>6.9967</v>
       </c>
       <c r="T15" t="n">
-        <v>-6.1309</v>
+        <v>5.1684</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3938</v>
+        <v>1.8283</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9492000000000004</v>
+        <v>-11.014</v>
       </c>
       <c r="W15" t="n">
-        <v>8.5885</v>
+        <v>-0.4875999999999998</v>
       </c>
       <c r="X15" t="n">
-        <v>-7.6394</v>
+        <v>-10.5261</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. ROBERTO JUREVICIUS</t>
+          <t>J. ROMERA GALINDO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.8392</v>
+        <v>-1.6616</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.1593</v>
+        <v>-1.1188</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.6798</v>
+        <v>-0.5428999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.8853</v>
+        <v>-1.9915</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2696999999999999</v>
+        <v>-1.4882</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.6156</v>
+        <v>-0.5032</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5936</v>
+        <v>-1.132</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0279</v>
+        <v>-0.5327</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.6215</v>
+        <v>-0.5994</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.2917</v>
+        <v>-0.8594999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2975</v>
+        <v>-0.9555</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9942000000000001</v>
+        <v>0.09610000000000002</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3824</v>
+        <v>0.9163</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.2987</v>
+        <v>0.9163</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.8199</v>
+        <v>-0.5865</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.5603</v>
+        <v>0.01319999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2596</v>
+        <v>-0.5997</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.5163</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.9108</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.4271</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. HOYAS PEREZ</t>
+          <t>J. ROBERTO JUREVICIUS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>-5.283499999999998</v>
+        <v>-2.4455</v>
       </c>
       <c r="E17" t="n">
-        <v>-6.608400000000001</v>
+        <v>-0.08769999999999989</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3248</v>
+        <v>-2.3578</v>
       </c>
       <c r="G17" t="n">
-        <v>-7.183000000000001</v>
+        <v>-2.8853</v>
       </c>
       <c r="H17" t="n">
-        <v>-11.2302</v>
+        <v>-0.2696999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>4.047699999999999</v>
+        <v>-2.6156</v>
       </c>
       <c r="J17" t="n">
-        <v>11.6564</v>
+        <v>-0.5936</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5519000000000014</v>
+        <v>1.0279</v>
       </c>
       <c r="L17" t="n">
-        <v>11.1045</v>
+        <v>-1.6215</v>
       </c>
       <c r="M17" t="n">
-        <v>-18.839</v>
+        <v>-2.2917</v>
       </c>
       <c r="N17" t="n">
-        <v>-11.7822</v>
+        <v>-1.2975</v>
       </c>
       <c r="O17" t="n">
-        <v>-7.0567</v>
+        <v>-0.9942000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.3822</v>
+        <v>2.3824</v>
       </c>
       <c r="Q17" t="n">
-        <v>-33.9029</v>
+        <v>-0.9163</v>
       </c>
       <c r="R17" t="n">
-        <v>31.52</v>
+        <v>3.2987</v>
       </c>
       <c r="S17" t="n">
-        <v>-8.5212</v>
+        <v>-0.4262</v>
       </c>
       <c r="T17" t="n">
-        <v>-7.9467</v>
+        <v>-0.4887</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5743999999999998</v>
+        <v>0.06240000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>12.8027</v>
+        <v>-1.5163</v>
       </c>
       <c r="W17" t="n">
-        <v>23.5844</v>
+        <v>1.9108</v>
       </c>
       <c r="X17" t="n">
-        <v>-10.7817</v>
+        <v>-3.4271</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. CAMPOS MONTEIRO</t>
+          <t>J. ROIG MESA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D18" t="n">
-        <v>-7.8445</v>
+        <v>-5.2243</v>
       </c>
       <c r="E18" t="n">
-        <v>-7.0716</v>
+        <v>-6.438199999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7731</v>
+        <v>1.2141</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.6878</v>
+        <v>-6.870699999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.3323</v>
+        <v>-2.0776</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3555</v>
+        <v>-4.793</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.7056</v>
+        <v>6.336</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.2607</v>
+        <v>6.1571</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.4452</v>
+        <v>0.1785000000000002</v>
       </c>
       <c r="M18" t="n">
-        <v>0.01780000000000004</v>
+        <v>-13.2061</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0717</v>
+        <v>-8.234500000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>1.0896</v>
+        <v>-4.9718</v>
       </c>
       <c r="P18" t="n">
-        <v>2.0159</v>
+        <v>7.696899999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0996</v>
+        <v>-13.5612</v>
       </c>
       <c r="R18" t="n">
-        <v>3.1154</v>
+        <v>21.2576</v>
       </c>
       <c r="S18" t="n">
-        <v>-3.2617</v>
+        <v>1.1509</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2663</v>
+        <v>0.1226000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.9956</v>
+        <v>1.0283</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.9109</v>
+        <v>-7.201</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.6646000000000001</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.9109</v>
+        <v>-7.8657</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. ROIG MESA</t>
+          <t>E. CAMPOS MONTEIRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>-12.8648</v>
+        <v>-6.2829</v>
       </c>
       <c r="E19" t="n">
-        <v>-10.0106</v>
+        <v>-6.0139</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.8544</v>
+        <v>-0.2688999999999998</v>
       </c>
       <c r="G19" t="n">
-        <v>-6.870699999999999</v>
+        <v>-4.6878</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.0776</v>
+        <v>-3.3323</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.793</v>
+        <v>-1.3555</v>
       </c>
       <c r="J19" t="n">
-        <v>6.336</v>
+        <v>-4.7056</v>
       </c>
       <c r="K19" t="n">
-        <v>6.1571</v>
+        <v>-2.2607</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1785000000000002</v>
+        <v>-2.4452</v>
       </c>
       <c r="M19" t="n">
-        <v>-13.2061</v>
+        <v>0.01780000000000004</v>
       </c>
       <c r="N19" t="n">
-        <v>-8.234500000000001</v>
+        <v>-1.0717</v>
       </c>
       <c r="O19" t="n">
-        <v>-4.9718</v>
+        <v>1.0896</v>
       </c>
       <c r="P19" t="n">
-        <v>7.696899999999999</v>
+        <v>2.0159</v>
       </c>
       <c r="Q19" t="n">
-        <v>-13.5612</v>
+        <v>-1.0996</v>
       </c>
       <c r="R19" t="n">
-        <v>21.2576</v>
+        <v>3.1154</v>
       </c>
       <c r="S19" t="n">
-        <v>-6.49</v>
+        <v>-1.6998</v>
       </c>
       <c r="T19" t="n">
-        <v>-3.4499</v>
+        <v>-0.2085</v>
       </c>
       <c r="U19" t="n">
-        <v>-3.0401</v>
+        <v>-1.4913</v>
       </c>
       <c r="V19" t="n">
-        <v>-7.201</v>
+        <v>-1.9109</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6646000000000001</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-7.8657</v>
+        <v>-1.9109</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>25</v>
       </c>
       <c r="D20" t="n">
-        <v>-14.8886</v>
+        <v>-18.1395</v>
       </c>
       <c r="E20" t="n">
-        <v>-33.8296</v>
+        <v>-39.1021</v>
       </c>
       <c r="F20" t="n">
-        <v>18.9408</v>
+        <v>20.963</v>
       </c>
       <c r="G20" t="n">
         <v>-36.1783</v>
@@ -2014,13 +2014,13 @@
         <v>51.8617</v>
       </c>
       <c r="S20" t="n">
-        <v>13.3292</v>
+        <v>10.0785</v>
       </c>
       <c r="T20" t="n">
-        <v>7.4546</v>
+        <v>2.1816</v>
       </c>
       <c r="U20" t="n">
-        <v>5.8748</v>
+        <v>7.8966</v>
       </c>
       <c r="V20" t="n">
         <v>2.646199999999999</v>
@@ -2047,13 +2047,13 @@
         <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>-17.3188</v>
+        <v>-18.3484</v>
       </c>
       <c r="E21" t="n">
-        <v>-11.2698</v>
+        <v>-12.2585</v>
       </c>
       <c r="F21" t="n">
-        <v>-6.048999999999999</v>
+        <v>-6.0898</v>
       </c>
       <c r="G21" t="n">
         <v>-14.4472</v>
@@ -2092,13 +2092,13 @@
         <v>7.879899999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1333</v>
+        <v>-2.1628</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1375000000000002</v>
+        <v>-0.8514000000000002</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.2707</v>
+        <v>-1.3116</v>
       </c>
       <c r="V21" t="n">
         <v>0.644</v>
@@ -2125,19 +2125,19 @@
         <v>26</v>
       </c>
       <c r="D22" t="n">
-        <v>171.6967</v>
+        <v>194.7883</v>
       </c>
       <c r="E22" t="n">
-        <v>36.68110000000001</v>
+        <v>44.38980000000002</v>
       </c>
       <c r="F22" t="n">
-        <v>135.0153</v>
+        <v>150.4008</v>
       </c>
       <c r="G22" t="n">
         <v>88.31140000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>75.49539999999999</v>
+        <v>75.4954</v>
       </c>
       <c r="I22" t="n">
         <v>12.8171</v>
@@ -2170,13 +2170,13 @@
         <v>420.5743000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>23.548</v>
+        <v>46.64019999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-4.8474</v>
+        <v>2.859299999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>28.3964</v>
+        <v>43.7804</v>
       </c>
       <c r="V22" t="n">
         <v>13.1063</v>
